--- a/outputs/excel/energy_rates.xlsx
+++ b/outputs/excel/energy_rates.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power Your Tomorrow Fixed - 6</t>
+          <t>Power Your Tomorrow Fixed - 3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$0.10070</t>
+          <t>$0.12970</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,42 +536,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SmartEnergy -  Web Only Rate</t>
+          <t>Simple Power 12 - Residential</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SmartEnergy</t>
+          <t>ENH Power</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$0.10900</t>
+          <t>$0.13900</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$100.00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1-800-760-1207</t>
+          <t>1-833-488-3147</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;a href="http://account.smartenergy.com/new-hampshire?utm_source=PUC_Site_NH&amp;utm_medium=referral&amp;utm_campaign=exclusive_online_rate" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -583,42 +583,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Embrace Green 6</t>
+          <t>Power Your Today Variable - 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$0.10990</t>
+          <t>$0.13970</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$50.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -630,22 +630,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Live Brighter SS 6</t>
+          <t>Power Your Tomorrow Fixed - 24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$0.11090</t>
+          <t>$0.13970</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power Your Today Variable - 1</t>
+          <t>Power Your Tomorrow Fixed - 14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$0.11260</t>
+          <t>$0.13970</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -724,42 +724,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Easy Choice 3 - Residential</t>
+          <t>Embrace Green 24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ENH Power</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$0.11290</t>
+          <t>$0.13990</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$150.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1-833-488-3147</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -771,22 +771,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Power Your Today Variable - 1 Green</t>
+          <t>Simply Clean 12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>CleanChoice Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$0.12260</t>
+          <t>$0.14000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>1-800-460-4900</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://mycleanchoice.com/nhshopperbh1" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Live Brighter AE 7</t>
+          <t>Live Brighter AE 35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$0.12290</t>
+          <t>$0.14290</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -865,22 +865,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>White Mountain Select 12 Month Term</t>
+          <t>Live Brighter SS 35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$0.13090</t>
+          <t>$0.14390</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -912,22 +912,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Power Your Today Fixed - 6</t>
+          <t>Live Brighter TO 35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town Square Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$0.13140</t>
+          <t>$0.14490</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1-877-430-0093</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -959,22 +959,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16 Month Standard Fixed</t>
+          <t>Live Brighter AE 12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>North American Power &amp; Gas, LLC</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$0.13290</t>
+          <t>$0.14490</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -984,17 +984,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>877-572-9965</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1006,7 +1006,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Embrace Green 24</t>
+          <t>Embrace Green 12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$0.13290</t>
+          <t>$0.14690</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$150.00</t>
+          <t>$75.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Live Brighter AE 13</t>
+          <t>Live Brighter 12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$0.13490</t>
+          <t>$0.14690</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1100,42 +1100,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Embrace Green 12</t>
+          <t>Live Brighter 24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CleanSky Energy</t>
+          <t>Direct Energy Services, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$0.13490</t>
+          <t>$0.14890</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-888-355-6205</t>
+          <t>888-836-6141</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1147,27 +1147,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ultimate Perks 12</t>
+          <t>Power Your Today Variable - 1 Green</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$0.13590</t>
+          <t>$0.14970</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1194,22 +1194,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14 Month Standard Fixed</t>
+          <t>White Mountain Select 12 Month Term</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>North American Power &amp; Gas, LLC</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$0.13590</t>
+          <t>$0.15200</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$10.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>877-572-9965</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.napower.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1241,17 +1241,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Simply Clean 12</t>
+          <t>SmartEnergy -  Web Only Rate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CleanChoice Energy</t>
+          <t>SmartEnergy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$0.13600</t>
+          <t>$0.15300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1-800-460-4900</t>
+          <t>1-800-760-1207</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>&lt;a href="http://mycleanchoice.com/nhshoppera12" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://smartenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Live Brighter 11</t>
+          <t>Go Green Lights 24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$0.14290</t>
+          <t>$0.15490</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1335,22 +1335,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Live Brighter 23</t>
+          <t>SureLock 12 - Residential</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$0.14290</t>
+          <t>$0.15490</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$110.00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1382,22 +1382,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Simple Power 12 - Residential</t>
+          <t>SureLock 24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENH Power</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$0.14290</t>
+          <t>$0.15590</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>$100.00</t>
+          <t>$200.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1-833-488-3147</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.providerpower.com/nh/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SureLock 12 - Residential</t>
+          <t>SimpleClean12 - Residential</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$0.14490</t>
+          <t>$0.15690</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1476,22 +1476,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SureLock 24</t>
+          <t>Ultimate Perks 12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$0.14590</t>
+          <t>$0.15700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>$200.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1523,17 +1523,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SimpleClean12 - Residential</t>
+          <t>Think Clean 12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Think Energy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$0.14690</t>
+          <t>$0.16100</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1543,22 +1543,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-833-669-3080</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1570,22 +1570,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Live Brighter TO 9</t>
+          <t>RescueLock 12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$0.14690</t>
+          <t>$0.16290</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$110.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1617,27 +1617,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Go Green Lights 8</t>
+          <t>SimpleClean</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Direct Energy Services, LLC</t>
+          <t>XOOM Energy New Hampshire, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$0.14790</t>
+          <t>$0.16490</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>888-836-6141</t>
+          <t>1-888-997-8979</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>&lt;a href="http://shop.directenergy.com/usn/product-chart/?msid=6338" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1664,22 +1664,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Think Clean 12</t>
+          <t>Embrace Green 6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>CleanSky Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$0.14800</t>
+          <t>$0.17990</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>$50.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>1-888-355-6205</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://cleanskyenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Think Clean 24</t>
+          <t>Winter Break 12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Think Energy</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$0.14900</t>
+          <t>$0.19700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1-833-669-3080</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.thinkenergy.com/?utm_source=rateboard&amp;utm_medium=referral&amp;utm_campaign=newhampshire" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1758,22 +1758,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RescueLock 12</t>
+          <t>Winter Break 24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>Ambit Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$0.15190</t>
+          <t>$0.20200</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-877-282-6248</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Power Your Today Fixed - 6 Green</t>
+          <t>Power Your Today Fixed - 6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$0.15880</t>
+          <t>$0.20710</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1852,27 +1852,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SimpleClean</t>
+          <t>SmartEnergy -  $100 Prepaid Card</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>XOOM Energy New Hampshire, LLC</t>
+          <t>SmartEnergy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$0.16490</t>
+          <t>$0.22400</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1-888-997-8979</t>
+          <t>1-800-760-1207</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;a href="http://www.xoomenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://smartenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1899,27 +1899,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Winter Break 12</t>
+          <t>Power Your Today Fixed - 6 Green</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ambit Energy</t>
+          <t>Town Square Energy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$0.17290</t>
+          <t>$0.23450</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1929,62 +1929,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1-877-282-6248</t>
+          <t>1-877-430-0093</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
+          <t>&lt;a href="http://www.townsquareenergy.com" target="_blank"&gt;Sign up&lt;/a&gt;</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Winter Break 24</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ambit Energy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>$0.17790</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1-877-282-6248</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>&lt;a href="http://ww2.ambitenergy.com/" target="_blank"&gt;Sign up&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>&lt;a href="https://www.energy.nh.gov/consumers/choosing-energy-supplier/choosing-energy-supplier-frequently-asked-questions" target="_blank"&gt;Learn more&lt;/a&gt;</t>
         </is>
